--- a/docs/superpowers/specs/2026-06-19-申通新格式映射-最终版.xlsx
+++ b/docs/superpowers/specs/2026-06-19-申通新格式映射-最终版.xlsx
@@ -53,12 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>03.04</t>
+          <t>03.02</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>申通APP购买单号</t>
+          <t>业务星计划奖励</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1504,373 +1504,381 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>54010101</t>
+          <t>54010208</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>面单费</t>
+          <t>小件员权益</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>700341</v>
+        <v>700349</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4057.9</v>
+        <v>0</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0</v>
+        <v>8048.23</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>资金类→损益</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr"/>
+          <t>负数冲减</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>负数，减少收入</t>
+        </is>
+      </c>
       <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="3" t="inlineStr"/>
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>03.33</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>智能遗失理赔</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>03.04</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>申通APP购买单号</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>资金往来</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>54010701</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>客服赔款</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>700382</v>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>54010101</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>面单费</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>700341</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="K17" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>714.11</v>
-      </c>
-      <c r="M17" s="4" t="n">
+      <c r="K17" s="5" t="n">
+        <v>272</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>4057.9</v>
+      </c>
+      <c r="M17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>资金类→损益</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr"/>
       <c r="Q17" s="3" t="inlineStr"/>
       <c r="R17" s="3" t="inlineStr"/>
       <c r="S17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>03.34</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>03.33</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>智能遗失理赔</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>资金往来</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>54010206</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>按需派费</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>700347</v>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="L18" s="4" t="n">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>54010701</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>客服赔款</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>700382</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>714.11</v>
+      </c>
+      <c r="M18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="4" t="n">
-        <v>68710.23</v>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>资金类→损益</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>按需派送直达</t>
-        </is>
-      </c>
+      <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="3" t="inlineStr"/>
       <c r="Q18" s="3" t="inlineStr"/>
       <c r="R18" s="3" t="inlineStr"/>
       <c r="S18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>03.63</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>网点保险代扣</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>03.34</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>资金往来</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>5601010402</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>商业保险</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>700421</v>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>54010206</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>按需派费</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>700347</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="K19" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>13454</v>
-      </c>
-      <c r="M19" s="4" t="n">
+      <c r="K19" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="L19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="M19" s="5" t="n">
+        <v>68710.23</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>资金类→损益</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>按需派送直达</t>
+        </is>
+      </c>
       <c r="P19" s="3" t="inlineStr"/>
       <c r="Q19" s="3" t="inlineStr"/>
       <c r="R19" s="3" t="inlineStr"/>
       <c r="S19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>03.73</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>网点三件理赔</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>03.63</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>网点保险代扣</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>资金往来</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>54010701</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>客服赔款</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>700382</v>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>CMB</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>323</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>574.51</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>13743.44</v>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>5601010402</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>商业保险</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>700421</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>13454</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>资金类→损益</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr"/>
       <c r="Q20" s="3" t="inlineStr"/>
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>030101</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>基础派费收费</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>总部应收</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>54010201</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>基础派费</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>700342</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>03.73</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>网点三件理赔</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>资金往来</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>54010701</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>客服赔款</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>700382</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>1278.2</v>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>CMB</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>323</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>574.51</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>13743.44</v>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>资金类→损益</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="3" t="inlineStr"/>
       <c r="Q21" s="3" t="inlineStr"/>
       <c r="R21" s="3" t="inlineStr"/>
@@ -1882,12 +1890,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>030102</t>
+          <t>030101</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>基础派费收费调整</t>
+          <t>基础派费收费</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1902,16 +1910,16 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54010205</t>
+          <t>54010201</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>调整派费</t>
+          <t>基础派费</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>700346</v>
+        <v>700342</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -1924,13 +1932,13 @@
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1062425.35</v>
+        <v>1278.2</v>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr"/>
@@ -1945,12 +1953,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>030103</t>
+          <t>030102</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>派费尾款</t>
+          <t>基础派费收费调整</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1965,16 +1973,16 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54010201</t>
+          <t>54010205</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>基础派费</t>
+          <t>调整派费</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>700342</v>
+        <v>700346</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -1987,13 +1995,13 @@
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3149.1</v>
+        <v>1062425.35</v>
       </c>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr"/>
@@ -2008,12 +2016,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>030111</t>
+          <t>030103</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>大货计重收费</t>
+          <t>派费尾款</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2028,16 +2036,16 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54010203</t>
+          <t>54010201</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>大货派费</t>
+          <t>基础派费</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>700344</v>
+        <v>700342</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -2050,13 +2058,13 @@
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>198</v>
+        <v>119</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>83.23</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>67538.57000000001</v>
+        <v>3149.1</v>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
@@ -2071,12 +2079,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>030112</t>
+          <t>030111</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>违规重量考核</t>
+          <t>大货计重收费</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2091,16 +2099,16 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54010603</t>
+          <t>54010203</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>操作规范考核</t>
+          <t>大货派费</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>700371</v>
+        <v>700344</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -2113,13 +2121,13 @@
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>83.23</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>69</v>
+        <v>67538.57000000001</v>
       </c>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
@@ -2134,12 +2142,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>030115</t>
+          <t>030112</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>乡镇村业务收费</t>
+          <t>违规重量考核</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2154,16 +2162,16 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54010207</t>
+          <t>54010603</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>扶持派费</t>
+          <t>操作规范考核</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>700348</v>
+        <v>700371</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -2176,13 +2184,13 @@
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>234</v>
+        <v>18</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5261.1</v>
+        <v>69</v>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr"/>
@@ -2197,12 +2205,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>030116</t>
+          <t>030115</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>大货操作费应收</t>
+          <t>乡镇村业务收费</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2217,16 +2225,16 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54010404</t>
+          <t>54010207</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>其他操作费</t>
+          <t>扶持派费</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>700362</v>
+        <v>700348</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -2239,13 +2247,13 @@
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>65</v>
+        <v>234</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>833.3</v>
+        <v>5261.1</v>
       </c>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
@@ -2260,12 +2268,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>030117</t>
+          <t>030116</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>周期性派费收费</t>
+          <t>大货操作费应收</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2280,16 +2288,16 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54010204</t>
+          <t>54010404</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>周期派费</t>
+          <t>其他操作费</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>700345</v>
+        <v>700362</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -2302,13 +2310,13 @@
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>546</v>
+        <v>833.3</v>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
@@ -2323,12 +2331,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>030253</t>
+          <t>030117</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>进港服务投诉考核</t>
+          <t>周期性派费收费</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2343,16 +2351,16 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>54010613</t>
+          <t>54010204</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>管控类罚款</t>
+          <t>周期派费</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>700381</v>
+        <v>700345</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
@@ -2361,17 +2369,17 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>32650</v>
+        <v>546</v>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
@@ -2381,67 +2389,67 @@
       <c r="S29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>030257</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>政策互惠</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>030234</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>星计划收费</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>总部应付</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>50010211</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>政策互惠</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>700318</v>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>54010208</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>小件员权益</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>700349</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="K30" s="5" t="n">
-        <v>172</v>
-      </c>
-      <c r="L30" s="5" t="n">
+      <c r="K30" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="5" t="n">
-        <v>228331</v>
-      </c>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="M30" s="4" t="n">
+        <v>29070.41</v>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>负数冲减</t>
         </is>
       </c>
-      <c r="O30" s="5" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>负数，减少收入</t>
         </is>
@@ -2452,260 +2460,276 @@
       <c r="S30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>030264</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>小件员直达派费</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>总部应付</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>50010208</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>小件员权益</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>700315</v>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>030253</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>进港服务投诉考核</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>总部应收</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>54010613</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>管控类罚款</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>700381</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="K31" s="5" t="n">
-        <v>178</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v>1684594</v>
-      </c>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t>负数冲减</t>
-        </is>
-      </c>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>负数，减少收入</t>
-        </is>
-      </c>
+      <c r="K31" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>32650</v>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr"/>
       <c r="Q31" s="3" t="inlineStr"/>
       <c r="R31" s="3" t="inlineStr"/>
       <c r="S31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>031008</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>批货收费</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>总部应收</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>54010404</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>其他操作费</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>700362</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>030257</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>政策互惠</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>总部应付</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>50010211</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>政策互惠</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>700318</v>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L32" s="2" t="n">
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="L32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="2" t="n">
-        <v>1308.63</v>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
+      <c r="M32" s="4" t="n">
+        <v>228331</v>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>负数冲减</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>负数，减少收入</t>
+        </is>
+      </c>
       <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="inlineStr"/>
       <c r="R32" s="3" t="inlineStr"/>
       <c r="S32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>040401</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>偷逃大货考核</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>总部应收</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>54010603</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>操作规范考核</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>700371</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>030264</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>小件员直达派费</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>总部应付</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>50010208</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>小件员权益</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>700315</v>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>1684594</v>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>负数冲减</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>负数，减少收入</t>
+        </is>
+      </c>
       <c r="P33" s="3" t="inlineStr"/>
       <c r="Q33" s="3" t="inlineStr"/>
       <c r="R33" s="3" t="inlineStr"/>
       <c r="S33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>040605</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>单件错发收费</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>总部应收</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>54010603</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>操作规范考核</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>700371</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>030270</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>派费直达服务费</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>总部应付</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>54010208</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>小件员权益</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>700349</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L34" s="2" t="n">
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="L34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
+      <c r="M34" s="4" t="n">
+        <v>95346.98</v>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>负数冲减</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>负数，减少收入</t>
+        </is>
+      </c>
       <c r="P34" s="3" t="inlineStr"/>
       <c r="Q34" s="3" t="inlineStr"/>
       <c r="R34" s="3" t="inlineStr"/>
@@ -2717,12 +2741,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>040606</t>
+          <t>031008</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>集包错发至网点收</t>
+          <t>批货收费</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2737,16 +2761,16 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>54010603</t>
+          <t>54010404</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>操作规范考核</t>
+          <t>其他操作费</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>700371</v>
+        <v>700362</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
@@ -2759,13 +2783,13 @@
         </is>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>192</v>
+        <v>1308.63</v>
       </c>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
@@ -2780,12 +2804,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>041207</t>
+          <t>040401</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>应集未集收</t>
+          <t>偷逃大货考核</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2822,13 +2846,13 @@
         </is>
       </c>
       <c r="K36" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>935</v>
+        <v>96.8</v>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr"/>
@@ -2843,12 +2867,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>041210</t>
+          <t>040605</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>票数不符收</t>
+          <t>单件错发收费</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2885,13 +2909,13 @@
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr"/>
@@ -2906,12 +2930,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>041214</t>
+          <t>040606</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>子母件收</t>
+          <t>集包错发至网点收</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2948,13 +2972,13 @@
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>400</v>
+        <v>192</v>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr"/>
@@ -2969,12 +2993,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>041901</t>
+          <t>041207</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>同行封装考核</t>
+          <t>应集未集收</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3011,13 +3035,13 @@
         </is>
       </c>
       <c r="K39" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2100</v>
+        <v>935</v>
       </c>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
@@ -3032,12 +3056,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>042013</t>
+          <t>041210</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>未打单退回考核</t>
+          <t>票数不符收</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3070,17 +3094,17 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
@@ -3095,12 +3119,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>042101</t>
+          <t>041214</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>网点车辆迟到考核</t>
+          <t>子母件收</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3115,16 +3139,16 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>54010605</t>
+          <t>54010603</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>车辆考核</t>
+          <t>操作规范考核</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>700373</v>
+        <v>700371</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
@@ -3137,13 +3161,13 @@
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr"/>
@@ -3158,12 +3182,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>042309</t>
+          <t>041901</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>中心禁限寄品收</t>
+          <t>同行封装考核</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3178,16 +3202,16 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>54010613</t>
+          <t>54010603</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>管控类罚款</t>
+          <t>操作规范考核</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>700381</v>
+        <v>700371</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -3200,13 +3224,13 @@
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>500</v>
+        <v>2100</v>
       </c>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
@@ -3221,12 +3245,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>043403</t>
+          <t>042013</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>回收面单使用考核</t>
+          <t>未打单退回考核</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3259,17 +3283,17 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>10.26</v>
+        <v>19</v>
       </c>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr"/>
@@ -3284,12 +3308,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>043601</t>
+          <t>042101</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>重复使用面单考核</t>
+          <t>网点车辆迟到考核</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3304,16 +3328,16 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>54010603</t>
+          <t>54010605</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>操作规范考核</t>
+          <t>车辆考核</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>700371</v>
+        <v>700373</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
@@ -3332,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr"/>
@@ -3347,12 +3371,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>043707</t>
+          <t>042309</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>分类错误收</t>
+          <t>中心禁限寄品收</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3367,16 +3391,16 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>54010603</t>
+          <t>54010613</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>操作规范考核</t>
+          <t>管控类罚款</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>700371</v>
+        <v>700381</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
@@ -3395,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
@@ -3410,12 +3434,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>043709</t>
+          <t>043403</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>异形件包装收</t>
+          <t>回收面单使用考核</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3452,13 +3476,13 @@
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>100</v>
+        <v>10.26</v>
       </c>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
@@ -3473,12 +3497,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>043715</t>
+          <t>043601</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>打印同行LOGO收</t>
+          <t>重复使用面单考核</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3515,13 +3539,13 @@
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>800</v>
+        <v>10</v>
       </c>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr"/>
@@ -3536,12 +3560,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>043723</t>
+          <t>043707</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>未贴安检贴收</t>
+          <t>分类错误收</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3556,16 +3580,16 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>54010613</t>
+          <t>54010603</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>管控类罚款</t>
+          <t>操作规范考核</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>700381</v>
+        <v>700371</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
@@ -3578,13 +3602,13 @@
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>720</v>
+        <v>200</v>
       </c>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr"/>
@@ -3599,12 +3623,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>043801</t>
+          <t>043709</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>物流信息完整性考核</t>
+          <t>异形件包装收</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3637,17 +3661,17 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2486.5</v>
+        <v>100</v>
       </c>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr"/>
@@ -3662,12 +3686,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>043803</t>
+          <t>043715</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>物流信息上传及时性考核</t>
+          <t>打印同行LOGO收</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3700,17 +3724,17 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K50" s="2" t="n">
-        <v>133</v>
+        <v>11</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1139.4</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4355.7</v>
+        <v>800</v>
       </c>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr"/>
@@ -3725,12 +3749,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>043806</t>
+          <t>043723</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>物流信息准确性考核</t>
+          <t>未贴安检贴收</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3745,16 +3769,16 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>54010603</t>
+          <t>54010613</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>操作规范考核</t>
+          <t>管控类罚款</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>700371</v>
+        <v>700381</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
@@ -3763,17 +3787,17 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K51" s="2" t="n">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>187.2</v>
+        <v>720</v>
       </c>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr"/>
@@ -3788,12 +3812,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>044001</t>
+          <t>043801</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>网点违规行为考核</t>
+          <t>物流信息完整性考核</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3808,16 +3832,16 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>54010613</t>
+          <t>54010603</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>管控类罚款</t>
+          <t>操作规范考核</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>700381</v>
+        <v>700371</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
@@ -3826,17 +3850,17 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K52" s="2" t="n">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3700</v>
+        <v>2486.5</v>
       </c>
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr"/>
@@ -3851,12 +3875,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>044208</t>
+          <t>043803</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>错交件应收</t>
+          <t>物流信息上传及时性考核</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3889,17 +3913,17 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K53" s="2" t="n">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1139.4</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>17650.5</v>
+        <v>4355.7</v>
       </c>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr"/>
@@ -3914,12 +3938,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>044306</t>
+          <t>043806</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>日托管服务收费</t>
+          <t>物流信息准确性考核</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3934,16 +3958,16 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>54010501</t>
+          <t>54010603</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>总部服务费</t>
+          <t>操作规范考核</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>700364</v>
+        <v>700371</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
@@ -3956,13 +3980,13 @@
         </is>
       </c>
       <c r="K54" s="2" t="n">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>8637.879999999999</v>
+        <v>187.2</v>
       </c>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr"/>
@@ -3977,12 +4001,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>044309</t>
+          <t>044001</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>拦截退回不及时考核收费</t>
+          <t>网点违规行为考核</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3997,16 +4021,16 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>54010602</t>
+          <t>54010613</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>时效考核</t>
+          <t>管控类罚款</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>700370</v>
+        <v>700381</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
@@ -4019,13 +4043,13 @@
         </is>
       </c>
       <c r="K55" s="2" t="n">
-        <v>142</v>
+        <v>4</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2223</v>
+        <v>3700</v>
       </c>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr"/>
@@ -4040,12 +4064,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>044311</t>
+          <t>044208</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>二三段码考核</t>
+          <t>错交件应收</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4078,17 +4102,17 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K56" s="2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1782.08</v>
+        <v>17650.5</v>
       </c>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr"/>
@@ -4103,12 +4127,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>050302</t>
+          <t>044306</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>梧桐短信提醒业务</t>
+          <t>日托管服务收费</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -4123,16 +4147,16 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>56020901</t>
+          <t>54010501</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>电话费</t>
+          <t>总部服务费</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>700412</v>
+        <v>700364</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4169,13 @@
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>444</v>
+        <v>172</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>11860.26</v>
+        <v>8637.879999999999</v>
       </c>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr"/>
@@ -4166,12 +4190,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>050503</t>
+          <t>044309</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>寄件手续费</t>
+          <t>拦截退回不及时考核收费</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4186,16 +4210,16 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>560302</t>
+          <t>54010602</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>手续费</t>
+          <t>时效考核</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>700272</v>
+        <v>700370</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
@@ -4204,17 +4228,17 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="K58" s="2" t="n">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>199.08</v>
+        <v>2223</v>
       </c>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr"/>
@@ -4224,67 +4248,63 @@
       <c r="S58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="n">
+      <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>050504</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>派件手续费</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>总部应付</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>54010501</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>总部服务费</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="n">
-        <v>700364</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>CMB</t>
-        </is>
-      </c>
-      <c r="K59" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="L59" s="6" t="n">
-        <v>240.91</v>
-      </c>
-      <c r="M59" s="6" t="n">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>044311</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>二三段码考核</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>总部应收</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>54010603</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>操作规范考核</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>700371</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N59" s="6" t="inlineStr">
-        <is>
-          <t>翻侧</t>
-        </is>
-      </c>
-      <c r="O59" s="6" t="inlineStr"/>
+      <c r="M59" s="2" t="n">
+        <v>1782.08</v>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
       <c r="P59" s="3" t="inlineStr"/>
       <c r="Q59" s="3" t="inlineStr"/>
       <c r="R59" s="3" t="inlineStr"/>
@@ -4296,12 +4316,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>051001</t>
+          <t>050302</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>退件操作费应收</t>
+          <t>梧桐短信提醒业务</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -4316,16 +4336,16 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>54010403</t>
+          <t>56020901</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>退件操作费</t>
+          <t>电话费</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>700361</v>
+        <v>700412</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
@@ -4334,17 +4354,17 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>111</v>
+        <v>444</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>34963.8</v>
+        <v>11860.26</v>
       </c>
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr"/>
@@ -4359,12 +4379,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>051101</t>
+          <t>050503</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>环保袋进港使用费</t>
+          <t>寄件手续费</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4379,16 +4399,16 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>54010802</t>
+          <t>560302</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>环保袋</t>
+          <t>手续费</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>700385</v>
+        <v>700272</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
@@ -4397,17 +4417,17 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K61" s="2" t="n">
-        <v>215</v>
+        <v>42</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>11190.75</v>
+        <v>199.08</v>
       </c>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr"/>
@@ -4417,63 +4437,67 @@
       <c r="S61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>051103</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>环保袋超时费</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>总部应收</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>54010802</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>环保袋</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>700385</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>050504</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>派件手续费</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>总部应付</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>54010501</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>总部服务费</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>700364</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
         <is>
           <t>CMB</t>
         </is>
       </c>
-      <c r="K62" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="L62" s="2" t="n">
+      <c r="K62" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="L62" s="6" t="n">
+        <v>240.91</v>
+      </c>
+      <c r="M62" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M62" s="2" t="n">
-        <v>2658.9</v>
-      </c>
-      <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr"/>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>翻侧</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="inlineStr"/>
       <c r="P62" s="3" t="inlineStr"/>
       <c r="Q62" s="3" t="inlineStr"/>
       <c r="R62" s="3" t="inlineStr"/>
@@ -4485,12 +4509,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>051104</t>
+          <t>051001</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>登记遗失费</t>
+          <t>退件操作费应收</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -4505,16 +4529,16 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>54010802</t>
+          <t>54010403</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>环保袋</t>
+          <t>退件操作费</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>700385</v>
+        <v>700361</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
@@ -4523,17 +4547,17 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>58.4</v>
+        <v>34963.8</v>
       </c>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr"/>
@@ -4548,12 +4572,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>051118</t>
+          <t>051101</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>网点未绑定包牌使用</t>
+          <t>环保袋进港使用费</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -4568,16 +4592,16 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>54010613</t>
+          <t>54010802</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>管控类罚款</t>
+          <t>环保袋</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>700381</v>
+        <v>700385</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
@@ -4586,17 +4610,17 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="K64" s="2" t="n">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>11190.75</v>
       </c>
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr"/>
@@ -4611,12 +4635,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>051123</t>
+          <t>051103</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>超时遗失费</t>
+          <t>环保袋超时费</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4653,13 +4677,13 @@
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1174.4</v>
+        <v>2658.9</v>
       </c>
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr"/>
@@ -4674,12 +4698,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>051126</t>
+          <t>051104</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>双面单收</t>
+          <t>登记遗失费</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4694,16 +4718,16 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>54010603</t>
+          <t>54010802</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>操作规范考核</t>
+          <t>环保袋</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>700371</v>
+        <v>700385</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -4712,17 +4736,17 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K66" s="2" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1470</v>
+        <v>58.4</v>
       </c>
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr"/>
@@ -4737,12 +4761,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>051641</t>
+          <t>051118</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>按需派送收费</t>
+          <t>网点未绑定包牌使用</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4757,16 +4781,16 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>54010206</t>
+          <t>54010613</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>按需派费</t>
+          <t>管控类罚款</t>
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>700347</v>
+        <v>700381</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -4779,13 +4803,13 @@
         </is>
       </c>
       <c r="K67" s="2" t="n">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1018.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr"/>
@@ -4800,12 +4824,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>051650</t>
+          <t>051123</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>充值手续费</t>
+          <t>超时遗失费</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4820,16 +4844,16 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>560302</t>
+          <t>54010802</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>手续费</t>
+          <t>环保袋</t>
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>700272</v>
+        <v>700385</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
@@ -4838,17 +4862,17 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>162.76</v>
+        <v>1174.4</v>
       </c>
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr"/>
@@ -4863,12 +4887,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>051651</t>
+          <t>051126</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>保价项目收费</t>
+          <t>双面单收</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4883,16 +4907,16 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>54010404</t>
+          <t>54010603</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>其他操作费</t>
+          <t>操作规范考核</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>700362</v>
+        <v>700371</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
@@ -4905,13 +4929,13 @@
         </is>
       </c>
       <c r="K69" s="2" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>79.3</v>
+        <v>1470</v>
       </c>
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr"/>
@@ -4926,12 +4950,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>051663</t>
+          <t>051641</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>淘逆业务收费-2小时</t>
+          <t>按需派送收费</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4946,16 +4970,16 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>54010404</t>
+          <t>54010206</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>其他操作费</t>
+          <t>按需派费</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>700362</v>
+        <v>700347</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
@@ -4968,13 +4992,13 @@
         </is>
       </c>
       <c r="K70" s="2" t="n">
-        <v>11</v>
+        <v>204</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>60.38</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1278.75</v>
+        <v>1018.7</v>
       </c>
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr"/>
@@ -4989,12 +5013,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>051667</t>
+          <t>051650</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>散件下游服务收费</t>
+          <t>充值手续费</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -5009,16 +5033,16 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>54010501</t>
+          <t>560302</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>总部服务费</t>
+          <t>手续费</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>700364</v>
+        <v>700272</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
@@ -5031,13 +5055,13 @@
         </is>
       </c>
       <c r="K71" s="2" t="n">
-        <v>319</v>
+        <v>87</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>7631.2</v>
+        <v>162.76</v>
       </c>
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr"/>
@@ -5052,12 +5076,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>051690</t>
+          <t>051651</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>按需派送考核</t>
+          <t>保价项目收费</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -5072,16 +5096,16 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>54010603</t>
+          <t>54010404</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>操作规范考核</t>
+          <t>其他操作费</t>
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>700371</v>
+        <v>700362</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
@@ -5090,17 +5114,17 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K72" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L72" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M72" s="2" t="n">
-        <v>17786</v>
+        <v>79.3</v>
       </c>
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr"/>
@@ -5115,12 +5139,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>051703</t>
+          <t>051663</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>市场客服收费-催揽考核</t>
+          <t>淘逆业务收费-2小时</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -5135,16 +5159,16 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>54010501</t>
+          <t>54010404</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>总部服务费</t>
+          <t>其他操作费</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>700364</v>
+        <v>700362</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
@@ -5157,13 +5181,13 @@
         </is>
       </c>
       <c r="K73" s="2" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>60.38</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1149.5</v>
+        <v>1278.75</v>
       </c>
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr"/>
@@ -5178,12 +5202,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>051707</t>
+          <t>051667</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>市场客服收费-转单兜底</t>
+          <t>散件下游服务收费</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -5220,13 +5244,13 @@
         </is>
       </c>
       <c r="K74" s="2" t="n">
-        <v>3</v>
+        <v>319</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>101.2</v>
+        <v>7631.2</v>
       </c>
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr"/>
@@ -5241,12 +5265,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>051709</t>
+          <t>051690</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>市场客服收费-爽约兜底</t>
+          <t>按需派送考核</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5261,16 +5285,16 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>54010501</t>
+          <t>54010603</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>总部服务费</t>
+          <t>操作规范考核</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>700364</v>
+        <v>700371</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
@@ -5279,17 +5303,17 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="K75" s="2" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2160</v>
+        <v>17786</v>
       </c>
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr"/>
@@ -5304,12 +5328,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>051711</t>
+          <t>051703</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>市场客服收费-工单兜底</t>
+          <t>市场客服收费-催揽考核</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -5346,13 +5370,13 @@
         </is>
       </c>
       <c r="K76" s="2" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2200</v>
+        <v>1149.5</v>
       </c>
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr"/>
@@ -5367,12 +5391,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>051801</t>
+          <t>051707</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>申鲜尊享项目收费</t>
+          <t>市场客服收费-转单兜底</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -5409,13 +5433,13 @@
         </is>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>20</v>
+        <v>101.2</v>
       </c>
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr"/>
@@ -5430,12 +5454,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>051903</t>
+          <t>051709</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>系统服务费</t>
+          <t>市场客服收费-爽约兜底</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -5450,16 +5474,16 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>54010505</t>
+          <t>54010501</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>信息技术服务费</t>
+          <t>总部服务费</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>700368</v>
+        <v>700364</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
@@ -5468,17 +5492,17 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K78" s="2" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>34000</v>
+        <v>2160</v>
       </c>
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr"/>
@@ -5493,12 +5517,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>052011</t>
+          <t>051711</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>提现服务费收费</t>
+          <t>市场客服收费-工单兜底</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -5513,16 +5537,16 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>560302</t>
+          <t>54010501</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>手续费</t>
+          <t>总部服务费</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>700272</v>
+        <v>700364</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
@@ -5531,17 +5555,17 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K79" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>840</v>
+        <v>2200</v>
       </c>
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr"/>
@@ -5556,12 +5580,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>060205</t>
+          <t>051801</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>面单服务收费</t>
+          <t>申鲜尊享项目收费</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -5576,16 +5600,16 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>54010101</t>
+          <t>54010501</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>面单费</t>
+          <t>总部服务费</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>700341</v>
+        <v>700364</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
@@ -5598,13 +5622,13 @@
         </is>
       </c>
       <c r="K80" s="2" t="n">
-        <v>234</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3068339.73</v>
+        <v>20</v>
       </c>
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr"/>
@@ -5619,12 +5643,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>060302</t>
+          <t>051903</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>辅料销售</t>
+          <t>系统服务费</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -5639,16 +5663,16 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>54010801</t>
+          <t>54010505</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>辅料</t>
+          <t>信息技术服务费</t>
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>700384</v>
+        <v>700368</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
@@ -5661,13 +5685,13 @@
         </is>
       </c>
       <c r="K81" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>43117.5</v>
+        <v>34000</v>
       </c>
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr"/>
@@ -5682,12 +5706,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>100101</t>
+          <t>052011</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>延误仲裁赔款</t>
+          <t>提现服务费收费</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5702,16 +5726,16 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>54010701</t>
+          <t>560302</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>客服赔款</t>
+          <t>手续费</t>
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>700382</v>
+        <v>700272</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
@@ -5720,17 +5744,17 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K82" s="2" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2190</v>
+        <v>840</v>
       </c>
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr"/>
@@ -5745,12 +5769,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>100201</t>
+          <t>060205</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>工单自动考核收费</t>
+          <t>面单服务收费</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5765,16 +5789,16 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>54010607</t>
+          <t>54010101</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>工单考核</t>
+          <t>面单费</t>
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>700375</v>
+        <v>700341</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
@@ -5783,17 +5807,17 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>178</v>
+        <v>234</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>3650</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>89840</v>
+        <v>3068339.73</v>
       </c>
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr"/>
@@ -5808,12 +5832,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>100301</t>
+          <t>060302</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>遗失仲裁赔款</t>
+          <t>辅料销售</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5828,16 +5852,16 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>54010701</t>
+          <t>54010801</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>客服赔款</t>
+          <t>辅料</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>700382</v>
+        <v>700384</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
@@ -5846,17 +5870,17 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>288.9</v>
+        <v>43117.5</v>
       </c>
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr"/>
@@ -5871,12 +5895,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>100401</t>
+          <t>100101</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>破损仲裁赔款</t>
+          <t>延误仲裁赔款</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5913,13 +5937,13 @@
         </is>
       </c>
       <c r="K85" s="2" t="n">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>35234.57</v>
+        <v>2190</v>
       </c>
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr"/>
@@ -5934,12 +5958,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>100601</t>
+          <t>100201</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>工单服务质量考核收费</t>
+          <t>工单自动考核收费</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5976,13 +6000,13 @@
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>3650</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>50170</v>
+        <v>89840</v>
       </c>
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr"/>
@@ -5997,12 +6021,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>100901</t>
+          <t>100301</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>先行理赔仲裁赔款</t>
+          <t>遗失仲裁赔款</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -6035,17 +6059,17 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="K87" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>318.93</v>
+        <v>288.9</v>
       </c>
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr"/>
@@ -6060,12 +6084,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>101003</t>
+          <t>100401</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>主动服务处理服务费</t>
+          <t>破损仲裁赔款</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -6080,16 +6104,16 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>54010501</t>
+          <t>54010701</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>总部服务费</t>
+          <t>客服赔款</t>
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>700364</v>
+        <v>700382</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
@@ -6098,17 +6122,17 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>5</v>
+        <v>35234.57</v>
       </c>
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr"/>
@@ -6123,12 +6147,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>101101</t>
+          <t>100601</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>超派件赔款</t>
+          <t>工单服务质量考核收费</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -6143,16 +6167,16 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>54010701</t>
+          <t>54010607</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>客服赔款</t>
+          <t>工单考核</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
-        <v>700382</v>
+        <v>700375</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
@@ -6161,17 +6185,17 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K89" s="2" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>101</v>
+        <v>50170</v>
       </c>
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr"/>
@@ -6186,12 +6210,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>101503</t>
+          <t>100901</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>签收率未达标收费</t>
+          <t>先行理赔仲裁赔款</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -6206,16 +6230,16 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>54010608</t>
+          <t>54010701</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>签收率考核</t>
+          <t>客服赔款</t>
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>700376</v>
+        <v>700382</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
@@ -6224,17 +6248,17 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K90" s="2" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8685</v>
+        <v>318.93</v>
       </c>
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr"/>
@@ -6249,12 +6273,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>101901</t>
+          <t>101003</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>电话接听服务费</t>
+          <t>主动服务处理服务费</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -6269,16 +6293,16 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>56020901</t>
+          <t>54010501</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>电话费</t>
+          <t>总部服务费</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>700412</v>
+        <v>700364</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
@@ -6291,13 +6315,13 @@
         </is>
       </c>
       <c r="K91" s="2" t="n">
-        <v>171</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3792</v>
+        <v>5</v>
       </c>
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr"/>
@@ -6312,12 +6336,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>110413</t>
+          <t>101101</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>客服综合考核</t>
+          <t>超派件赔款</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -6332,16 +6356,16 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>54010604</t>
+          <t>54010701</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>客服类考核</t>
+          <t>客服赔款</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>700372</v>
+        <v>700382</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
@@ -6350,17 +6374,17 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K92" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5750</v>
+        <v>101</v>
       </c>
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr"/>
@@ -6375,12 +6399,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>110420</t>
+          <t>101503</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>省区综合考核收费</t>
+          <t>签收率未达标收费</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -6395,16 +6419,16 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>54010612</t>
+          <t>54010608</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>省区综合考核</t>
+          <t>签收率考核</t>
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>700380</v>
+        <v>700376</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
@@ -6413,17 +6437,17 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="K93" s="2" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>519</v>
+        <v>8685</v>
       </c>
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr"/>
@@ -6438,12 +6462,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>110437</t>
+          <t>101901</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>实名制考核收费</t>
+          <t>电话接听服务费</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -6458,16 +6482,16 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>54010613</t>
+          <t>56020901</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>管控类罚款</t>
+          <t>电话费</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>700381</v>
+        <v>700412</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
@@ -6476,17 +6500,17 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K94" s="2" t="n">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>965</v>
+        <v>3792</v>
       </c>
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr"/>
@@ -6501,12 +6525,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>110474</t>
+          <t>110413</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>操作综合考核赔款</t>
+          <t>客服综合考核</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -6521,16 +6545,16 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>54010603</t>
+          <t>54010604</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>操作规范考核</t>
+          <t>客服类考核</t>
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>700371</v>
+        <v>700372</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
@@ -6543,13 +6567,13 @@
         </is>
       </c>
       <c r="K95" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1300</v>
+        <v>5750</v>
       </c>
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr"/>
@@ -6564,12 +6588,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>110489</t>
+          <t>110420</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>揽收超48h滞留考核</t>
+          <t>省区综合考核收费</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -6584,16 +6608,16 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>54010602</t>
+          <t>54010612</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>时效考核</t>
+          <t>省区综合考核</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>700370</v>
+        <v>700380</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
@@ -6602,17 +6626,17 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K96" s="2" t="n">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3464</v>
+        <v>519</v>
       </c>
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr"/>
@@ -6627,12 +6651,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>110492</t>
+          <t>110437</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>虚假问题件考核</t>
+          <t>实名制考核收费</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -6647,16 +6671,16 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>54010610</t>
+          <t>54010613</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>虚假问题件考核</t>
+          <t>管控类罚款</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>700378</v>
+        <v>700381</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
@@ -6665,17 +6689,17 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K97" s="2" t="n">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4495</v>
+        <v>965</v>
       </c>
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr"/>
@@ -6690,12 +6714,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>110496</t>
+          <t>110474</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>交货滞留考核</t>
+          <t>操作综合考核赔款</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -6710,16 +6734,16 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>54010602</t>
+          <t>54010603</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>时效考核</t>
+          <t>操作规范考核</t>
         </is>
       </c>
       <c r="H98" s="2" t="n">
-        <v>700370</v>
+        <v>700371</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
@@ -6728,17 +6752,17 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K98" s="2" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>36564.5</v>
+        <v>1300</v>
       </c>
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr"/>
@@ -6753,12 +6777,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>110498</t>
+          <t>110489</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>揽收不及时考核-淘天</t>
+          <t>揽收超48h滞留考核</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -6795,13 +6819,13 @@
         </is>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>155</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>403</v>
+        <v>3464</v>
       </c>
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr"/>
@@ -6816,12 +6840,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>110901</t>
+          <t>110492</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>网点租金</t>
+          <t>虚假问题件考核</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -6836,16 +6860,16 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>54010610</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>租金</t>
+          <t>虚假问题件考核</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>700250</v>
+        <v>700378</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
@@ -6854,17 +6878,17 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K100" s="2" t="n">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10320</v>
+        <v>4495</v>
       </c>
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr"/>
@@ -6879,12 +6903,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>110903</t>
+          <t>110496</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>网点水电费收</t>
+          <t>交货滞留考核</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -6899,16 +6923,16 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>560205</t>
+          <t>54010602</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>水电费</t>
+          <t>时效考核</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>700251</v>
+        <v>700370</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
@@ -6917,17 +6941,17 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K101" s="2" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1000</v>
+        <v>36564.5</v>
       </c>
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr"/>
@@ -6942,12 +6966,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>110929</t>
+          <t>110498</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>末端考核</t>
+          <t>揽收不及时考核-淘天</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -6962,16 +6986,16 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>54010611</t>
+          <t>54010602</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>末端类考核</t>
+          <t>时效考核</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>700379</v>
+        <v>700370</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
@@ -6980,17 +7004,17 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>6033.38</v>
+        <v>403</v>
       </c>
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr"/>
@@ -7005,12 +7029,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>110937</t>
+          <t>110901</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>工服打卡考核收费</t>
+          <t>网点租金</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -7025,16 +7049,16 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>54010613</t>
+          <t>560204</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>管控类罚款</t>
+          <t>租金</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
-        <v>700381</v>
+        <v>700250</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
@@ -7047,13 +7071,13 @@
         </is>
       </c>
       <c r="K103" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3460</v>
+        <v>10320</v>
       </c>
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr"/>
@@ -7068,12 +7092,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>110938</t>
+          <t>110903</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>网点出仓率考核收费</t>
+          <t>网点水电费收</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -7088,16 +7112,16 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>54010606</t>
+          <t>560205</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>网管类考核</t>
+          <t>水电费</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>700374</v>
+        <v>700251</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
@@ -7110,13 +7134,13 @@
         </is>
       </c>
       <c r="K104" s="2" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>5280.46</v>
+        <v>1000</v>
       </c>
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr"/>
@@ -7131,12 +7155,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>110940</t>
+          <t>110929</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>GPS基础服务费</t>
+          <t>末端考核</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -7151,16 +7175,16 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>54010505</t>
+          <t>54010611</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>信息技术服务费</t>
+          <t>末端类考核</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
-        <v>700368</v>
+        <v>700379</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
@@ -7169,17 +7193,17 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>200</v>
+        <v>6033.38</v>
       </c>
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr"/>
@@ -7194,12 +7218,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>110943</t>
+          <t>110937</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>喵柜考核</t>
+          <t>工服打卡考核收费</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -7214,16 +7238,16 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>54010611</t>
+          <t>54010613</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>末端类考核</t>
+          <t>管控类罚款</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>700379</v>
+        <v>700381</v>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
@@ -7236,13 +7260,13 @@
         </is>
       </c>
       <c r="K106" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3800</v>
+        <v>3460</v>
       </c>
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr"/>
@@ -7257,12 +7281,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>201008</t>
+          <t>110938</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>环保袋出港使用费</t>
+          <t>网点出仓率考核收费</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -7277,16 +7301,16 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>54010802</t>
+          <t>54010606</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>环保袋</t>
+          <t>网管类考核</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>700385</v>
+        <v>700374</v>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
@@ -7295,17 +7319,17 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="K107" s="2" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>7646</v>
+        <v>5280.46</v>
       </c>
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr"/>
@@ -7315,67 +7339,63 @@
       <c r="S107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="n">
+      <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>3.28</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr"/>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>资金往来</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>54010701</t>
-        </is>
-      </c>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>客服赔款</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="n">
-        <v>700382</v>
-      </c>
-      <c r="I108" s="4" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>110940</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>GPS基础服务费</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>总部应收</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>54010505</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>信息技术服务费</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>700368</v>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="K108" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L108" s="4" t="n">
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>CMB</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M108" s="4" t="n">
-        <v>11639.54</v>
-      </c>
-      <c r="N108" s="4" t="inlineStr">
-        <is>
-          <t>资金类→损益</t>
-        </is>
-      </c>
-      <c r="O108" s="4" t="inlineStr">
-        <is>
-          <t>菜鸟裹裹工单赔付账单</t>
-        </is>
-      </c>
+      <c r="M108" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="3" t="inlineStr"/>
       <c r="Q108" s="3" t="inlineStr"/>
       <c r="R108" s="3" t="inlineStr"/>
@@ -7387,12 +7407,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>301003</t>
+          <t>110943</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>外呼系统通讯费</t>
+          <t>喵柜考核</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -7407,16 +7427,16 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>56020901</t>
+          <t>54010611</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>电话费</t>
+          <t>末端类考核</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>700412</v>
+        <v>700379</v>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
@@ -7425,17 +7445,17 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="K109" s="2" t="n">
-        <v>168</v>
+        <v>3</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3122.43</v>
+        <v>3800</v>
       </c>
       <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr"/>
@@ -7450,12 +7470,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>301004</t>
+          <t>201008</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>呼叫系统通讯费</t>
+          <t>环保袋出港使用费</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -7470,16 +7490,16 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>56020901</t>
+          <t>54010802</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>电话费</t>
+          <t>环保袋</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>700412</v>
+        <v>700385</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -7488,17 +7508,17 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K110" s="2" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>58.77</v>
+        <v>7646</v>
       </c>
       <c r="N110" s="2" t="inlineStr"/>
       <c r="O110" s="2" t="inlineStr"/>
@@ -7508,63 +7528,67 @@
       <c r="S110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>301006</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>在线客服服务费</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>总部应收</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>54010501</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>总部服务费</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>700364</v>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr"/>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>资金往来</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>54010701</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>客服赔款</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>700382</v>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>CMB</t>
-        </is>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="L111" s="2" t="n">
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L111" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M111" s="2" t="n">
-        <v>5995</v>
-      </c>
-      <c r="N111" s="2" t="inlineStr"/>
-      <c r="O111" s="2" t="inlineStr"/>
+      <c r="M111" s="5" t="n">
+        <v>11639.54</v>
+      </c>
+      <c r="N111" s="5" t="inlineStr">
+        <is>
+          <t>资金类→损益</t>
+        </is>
+      </c>
+      <c r="O111" s="5" t="inlineStr">
+        <is>
+          <t>菜鸟裹裹工单赔付账单</t>
+        </is>
+      </c>
       <c r="P111" s="3" t="inlineStr"/>
       <c r="Q111" s="3" t="inlineStr"/>
       <c r="R111" s="3" t="inlineStr"/>
@@ -7576,12 +7600,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>301007</t>
+          <t>301003</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>三件仲裁申诉服务费</t>
+          <t>外呼系统通讯费</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -7596,16 +7620,16 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>54010501</t>
+          <t>56020901</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>总部服务费</t>
+          <t>电话费</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>700364</v>
+        <v>700412</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
@@ -7618,13 +7642,13 @@
         </is>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2</v>
+        <v>168</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M112" s="2" t="n">
-        <v>40</v>
+        <v>3122.43</v>
       </c>
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr"/>
@@ -7639,12 +7663,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>301008</t>
+          <t>301004</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>协作任务发起服务费</t>
+          <t>呼叫系统通讯费</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -7659,20 +7683,20 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>54010501</t>
+          <t>56020901</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>总部服务费</t>
+          <t>电话费</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>700364</v>
+        <v>700412</v>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -7681,13 +7705,13 @@
         </is>
       </c>
       <c r="K113" s="2" t="n">
-        <v>160</v>
+        <v>4</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>15267.3</v>
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>14380</v>
+        <v>58.77</v>
       </c>
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr"/>
@@ -7702,12 +7726,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>301009</t>
+          <t>301006</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>协作任务未解决服务费</t>
+          <t>在线客服服务费</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -7744,13 +7768,13 @@
         </is>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>50</v>
+        <v>5995</v>
       </c>
       <c r="N114" s="2" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr"/>
@@ -7765,12 +7789,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>301010</t>
+          <t>301007</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>协作任务服务费</t>
+          <t>三件仲裁申诉服务费</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -7807,13 +7831,13 @@
         </is>
       </c>
       <c r="K115" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M115" s="2" t="n">
-        <v>284</v>
+        <v>40</v>
       </c>
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr"/>
@@ -7828,12 +7852,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>301010</t>
+          <t>301008</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>协作任务超时服务费</t>
+          <t>协作任务发起服务费</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -7861,7 +7885,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -7870,13 +7894,13 @@
         </is>
       </c>
       <c r="K116" s="2" t="n">
-        <v>6</v>
+        <v>160</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0</v>
+        <v>15267.3</v>
       </c>
       <c r="M116" s="2" t="n">
-        <v>210</v>
+        <v>14380</v>
       </c>
       <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr"/>
@@ -7891,12 +7915,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>401001</t>
+          <t>301009</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>派费包差分摊</t>
+          <t>协作任务未解决服务费</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -7911,16 +7935,16 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>54010201</t>
+          <t>54010501</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>基础派费</t>
+          <t>总部服务费</t>
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>700342</v>
+        <v>700364</v>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
@@ -7929,17 +7953,17 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K117" s="2" t="n">
-        <v>132</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1836.84</v>
+        <v>50</v>
       </c>
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr"/>
@@ -7954,12 +7978,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>401002</t>
+          <t>301010</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>扶持派费收费</t>
+          <t>协作任务服务费</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -7974,16 +7998,16 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>54010207</t>
+          <t>54010501</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>扶持派费</t>
+          <t>总部服务费</t>
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>700348</v>
+        <v>700364</v>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
@@ -7992,17 +8016,17 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K118" s="2" t="n">
-        <v>259</v>
+        <v>4</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M118" s="2" t="n">
-        <v>144987.8</v>
+        <v>284</v>
       </c>
       <c r="N118" s="2" t="inlineStr"/>
       <c r="O118" s="2" t="inlineStr"/>
@@ -8017,12 +8041,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>401003</t>
+          <t>301010</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>无点收费</t>
+          <t>协作任务超时服务费</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -8037,16 +8061,16 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>54010201</t>
+          <t>54010501</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>基础派费</t>
+          <t>总部服务费</t>
         </is>
       </c>
       <c r="H119" s="2" t="n">
-        <v>700342</v>
+        <v>700364</v>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
@@ -8055,17 +8079,17 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K119" s="2" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1500</v>
+        <v>210</v>
       </c>
       <c r="N119" s="2" t="inlineStr"/>
       <c r="O119" s="2" t="inlineStr"/>
@@ -8080,12 +8104,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>401004</t>
+          <t>401001</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>派费预收</t>
+          <t>派费包差分摊</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -8122,13 +8146,13 @@
         </is>
       </c>
       <c r="K120" s="2" t="n">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2359000</v>
+        <v>1836.84</v>
       </c>
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr"/>
@@ -8143,12 +8167,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>501002</t>
+          <t>401002</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>燃油附加费</t>
+          <t>扶持派费收费</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -8163,16 +8187,16 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>54010901</t>
+          <t>54010207</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>燃油费</t>
+          <t>扶持派费</t>
         </is>
       </c>
       <c r="H121" s="2" t="n">
-        <v>700386</v>
+        <v>700348</v>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
@@ -8185,13 +8209,13 @@
         </is>
       </c>
       <c r="K121" s="2" t="n">
-        <v>172</v>
+        <v>259</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M121" s="2" t="n">
-        <v>170268.78</v>
+        <v>144987.8</v>
       </c>
       <c r="N121" s="2" t="inlineStr"/>
       <c r="O121" s="2" t="inlineStr"/>
@@ -8201,134 +8225,126 @@
       <c r="S121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="6" t="n">
+      <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>602004</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>其他服务费</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>总部应付</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>54010501</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>总部服务费</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="n">
-        <v>700364</v>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>401003</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>无点收费</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>总部应收</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>54010201</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>基础派费</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>700342</v>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J122" s="6" t="inlineStr">
+      <c r="J122" s="2" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="K122" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L122" s="6" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="M122" s="6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="N122" s="6" t="inlineStr">
-        <is>
-          <t>翻侧</t>
-        </is>
-      </c>
-      <c r="O122" s="6" t="inlineStr"/>
+      <c r="K122" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr"/>
       <c r="P122" s="3" t="inlineStr"/>
       <c r="Q122" s="3" t="inlineStr"/>
       <c r="R122" s="3" t="inlineStr"/>
       <c r="S122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="n">
+      <c r="A123" s="2" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>602007</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>揽件服务费</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>总部应付</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>54010501</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr">
-        <is>
-          <t>总部服务费</t>
-        </is>
-      </c>
-      <c r="H123" s="6" t="n">
-        <v>700364</v>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="J123" s="6" t="inlineStr">
-        <is>
-          <t>CMB</t>
-        </is>
-      </c>
-      <c r="K123" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L123" s="6" t="n">
-        <v>24439.49</v>
-      </c>
-      <c r="M123" s="6" t="n">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>401004</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>派费预收</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>总部应收</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>54010201</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>基础派费</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>700342</v>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="L123" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N123" s="6" t="inlineStr">
-        <is>
-          <t>翻侧</t>
-        </is>
-      </c>
-      <c r="O123" s="6" t="inlineStr"/>
+      <c r="M123" s="2" t="n">
+        <v>2359000</v>
+      </c>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr"/>
       <c r="P123" s="3" t="inlineStr"/>
       <c r="Q123" s="3" t="inlineStr"/>
       <c r="R123" s="3" t="inlineStr"/>
@@ -8340,12 +8356,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>602022</t>
+          <t>501002</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>托管服务费（大市场）</t>
+          <t>燃油附加费</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -8360,16 +8376,16 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>54010501</t>
+          <t>54010901</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>总部服务费</t>
+          <t>燃油费</t>
         </is>
       </c>
       <c r="H124" s="2" t="n">
-        <v>700364</v>
+        <v>700386</v>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
@@ -8378,17 +8394,17 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K124" s="2" t="n">
-        <v>4</v>
+        <v>172</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M124" s="2" t="n">
-        <v>385.41</v>
+        <v>170268.78</v>
       </c>
       <c r="N124" s="2" t="inlineStr"/>
       <c r="O124" s="2" t="inlineStr"/>
@@ -8403,12 +8419,12 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>602023</t>
+          <t>602004</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>大网考核</t>
+          <t>其他服务费</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -8423,16 +8439,16 @@
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>54010613</t>
+          <t>54010501</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>管控类罚款</t>
+          <t>总部服务费</t>
         </is>
       </c>
       <c r="H125" s="6" t="n">
-        <v>700381</v>
+        <v>700364</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -8441,17 +8457,17 @@
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="K125" s="6" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="L125" s="6" t="n">
-        <v>0</v>
+        <v>53.7</v>
       </c>
       <c r="M125" s="6" t="n">
-        <v>2053.99</v>
+        <v>1200</v>
       </c>
       <c r="N125" s="6" t="inlineStr">
         <is>
@@ -8470,12 +8486,12 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>602024</t>
+          <t>602007</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>对客理赔</t>
+          <t>揽件服务费</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -8490,35 +8506,35 @@
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>54010604</t>
+          <t>54010501</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>客服类考核</t>
+          <t>总部服务费</t>
         </is>
       </c>
       <c r="H126" s="6" t="n">
-        <v>700372</v>
+        <v>700364</v>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K126" s="6" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="L126" s="6" t="n">
+        <v>24439.49</v>
+      </c>
+      <c r="M126" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="M126" s="6" t="n">
-        <v>348652.91</v>
       </c>
       <c r="N126" s="6" t="inlineStr">
         <is>
@@ -8537,12 +8553,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>646001</t>
+          <t>602022</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>治理扣费</t>
+          <t>托管服务费（大市场）</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -8557,16 +8573,16 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>54010613</t>
+          <t>54010501</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>管控类罚款</t>
+          <t>总部服务费</t>
         </is>
       </c>
       <c r="H127" s="2" t="n">
-        <v>700381</v>
+        <v>700364</v>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
@@ -8575,17 +8591,17 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="K127" s="2" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M127" s="2" t="n">
-        <v>39745.14</v>
+        <v>385.41</v>
       </c>
       <c r="N127" s="2" t="inlineStr"/>
       <c r="O127" s="2" t="inlineStr"/>
@@ -8595,463 +8611,455 @@
       <c r="S127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="6" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>011116</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>异形件操作费付</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>602023</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>大网考核</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
         <is>
           <t>总部应付</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>贷</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>50010302</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>其他操作费</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>700320</v>
-      </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>54010613</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>管控类罚款</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="n">
+        <v>700381</v>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="K128" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="L128" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="M128" s="2" t="n">
+      <c r="K128" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="L128" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N128" s="2" t="inlineStr"/>
-      <c r="O128" s="2" t="inlineStr"/>
+      <c r="M128" s="6" t="n">
+        <v>2053.99</v>
+      </c>
+      <c r="N128" s="6" t="inlineStr">
+        <is>
+          <t>翻侧</t>
+        </is>
+      </c>
+      <c r="O128" s="6" t="inlineStr"/>
       <c r="P128" s="3" t="inlineStr"/>
       <c r="Q128" s="3" t="inlineStr"/>
       <c r="R128" s="3" t="inlineStr"/>
       <c r="S128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>011119</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>一口价补贴</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>602024</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>对客理赔</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
         <is>
           <t>总部应付</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>贷</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>50010501</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>政策返利</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>700322</v>
-      </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>54010604</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>客服类考核</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="n">
+        <v>700372</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="K129" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L129" s="2" t="n">
-        <v>149773.88</v>
-      </c>
-      <c r="M129" s="2" t="n">
-        <v>26519.1</v>
-      </c>
-      <c r="N129" s="2" t="inlineStr"/>
-      <c r="O129" s="2" t="inlineStr"/>
+      <c r="K129" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="L129" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="6" t="n">
+        <v>348652.91</v>
+      </c>
+      <c r="N129" s="6" t="inlineStr">
+        <is>
+          <t>翻侧</t>
+        </is>
+      </c>
+      <c r="O129" s="6" t="inlineStr"/>
       <c r="P129" s="3" t="inlineStr"/>
       <c r="Q129" s="3" t="inlineStr"/>
       <c r="R129" s="3" t="inlineStr"/>
       <c r="S129" s="3" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n">
+      <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>03.02</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>业务星计划奖励</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>资金往来</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>贷</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>54010208</t>
-        </is>
-      </c>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>小件员权益</t>
-        </is>
-      </c>
-      <c r="H130" s="5" t="n">
-        <v>700349</v>
-      </c>
-      <c r="I130" s="5" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>646001</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>治理扣费</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>总部应收</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>54010613</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>管控类罚款</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>700381</v>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J130" s="5" t="inlineStr">
+      <c r="J130" s="2" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="K130" s="5" t="n">
-        <v>239</v>
-      </c>
-      <c r="L130" s="5" t="n">
+      <c r="K130" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="L130" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M130" s="5" t="n">
-        <v>8048.23</v>
-      </c>
-      <c r="N130" s="5" t="inlineStr">
-        <is>
-          <t>负数冲减</t>
-        </is>
-      </c>
-      <c r="O130" s="5" t="inlineStr">
-        <is>
-          <t>负数，减少收入</t>
-        </is>
-      </c>
+      <c r="M130" s="2" t="n">
+        <v>39745.14</v>
+      </c>
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="3" t="inlineStr"/>
       <c r="Q130" s="3" t="inlineStr"/>
       <c r="R130" s="3" t="inlineStr"/>
       <c r="S130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="n">
+      <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>03.43</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr"/>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>资金往来</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>011116</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>异形件操作费付</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>总部应付</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>贷</t>
         </is>
       </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>50010104</t>
-        </is>
-      </c>
-      <c r="G131" s="4" t="inlineStr">
-        <is>
-          <t>总部平台单</t>
-        </is>
-      </c>
-      <c r="H131" s="4" t="n">
-        <v>700307</v>
-      </c>
-      <c r="I131" s="4" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="K131" s="4" t="n">
-        <v>223</v>
-      </c>
-      <c r="L131" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="M131" s="4" t="n">
-        <v>18980.77</v>
-      </c>
-      <c r="N131" s="4" t="inlineStr">
-        <is>
-          <t>资金类→损益</t>
-        </is>
-      </c>
-      <c r="O131" s="4" t="inlineStr">
-        <is>
-          <t>个人寄件业务</t>
-        </is>
-      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>50010302</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>其他操作费</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>700320</v>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="2" t="inlineStr"/>
+      <c r="O131" s="2" t="inlineStr"/>
       <c r="P131" s="3" t="inlineStr"/>
       <c r="Q131" s="3" t="inlineStr"/>
       <c r="R131" s="3" t="inlineStr"/>
       <c r="S131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="4" t="n">
+      <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>03.47</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr"/>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>资金往来</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>011119</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>一口价补贴</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>总部应付</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>贷</t>
         </is>
       </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>50010104</t>
-        </is>
-      </c>
-      <c r="G132" s="4" t="inlineStr">
-        <is>
-          <t>总部平台单</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="n">
-        <v>700307</v>
-      </c>
-      <c r="I132" s="4" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="J132" s="4" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>50010501</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>政策返利</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>700322</v>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="K132" s="4" t="n">
-        <v>172</v>
-      </c>
-      <c r="L132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" s="4" t="n">
-        <v>577528.54</v>
-      </c>
-      <c r="N132" s="4" t="inlineStr">
-        <is>
-          <t>资金类→损益</t>
-        </is>
-      </c>
-      <c r="O132" s="4" t="inlineStr">
-        <is>
-          <t>个人寄件三方渠道散件</t>
-        </is>
-      </c>
+      <c r="K132" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>149773.88</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>26519.1</v>
+      </c>
+      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr"/>
       <c r="P132" s="3" t="inlineStr"/>
       <c r="Q132" s="3" t="inlineStr"/>
       <c r="R132" s="3" t="inlineStr"/>
       <c r="S132" s="3" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="n">
+      <c r="A133" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>03.47</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>个人寄件-当日取揽件费</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>03.43</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr"/>
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>资金往来</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="E133" s="5" t="inlineStr">
         <is>
           <t>贷</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr">
+      <c r="F133" s="5" t="inlineStr">
         <is>
           <t>50010104</t>
         </is>
       </c>
-      <c r="G133" s="4" t="inlineStr">
+      <c r="G133" s="5" t="inlineStr">
         <is>
           <t>总部平台单</t>
         </is>
       </c>
-      <c r="H133" s="4" t="n">
+      <c r="H133" s="5" t="n">
         <v>700307</v>
       </c>
-      <c r="I133" s="4" t="inlineStr">
+      <c r="I133" s="5" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J133" s="4" t="inlineStr">
+      <c r="J133" s="5" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="K133" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" s="4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="N133" s="4" t="inlineStr">
+      <c r="K133" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="M133" s="5" t="n">
+        <v>18980.77</v>
+      </c>
+      <c r="N133" s="5" t="inlineStr">
         <is>
           <t>资金类→损益</t>
         </is>
       </c>
-      <c r="O133" s="4" t="inlineStr"/>
+      <c r="O133" s="5" t="inlineStr">
+        <is>
+          <t>个人寄件业务</t>
+        </is>
+      </c>
       <c r="P133" s="3" t="inlineStr"/>
       <c r="Q133" s="3" t="inlineStr"/>
       <c r="R133" s="3" t="inlineStr"/>
       <c r="S133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="n">
+      <c r="A134" s="5" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="4" t="inlineStr">
-        <is>
-          <t>03.49</t>
-        </is>
-      </c>
-      <c r="C134" s="4" t="inlineStr"/>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>03.47</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr"/>
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>资金往来</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
+      <c r="E134" s="5" t="inlineStr">
         <is>
           <t>贷</t>
         </is>
       </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>50010103</t>
-        </is>
-      </c>
-      <c r="G134" s="4" t="inlineStr">
-        <is>
-          <t>到付收入</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="n">
-        <v>700306</v>
-      </c>
-      <c r="I134" s="4" t="inlineStr">
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>50010104</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>总部平台单</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>700307</v>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>CMB</t>
-        </is>
-      </c>
-      <c r="K134" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="L134" s="4" t="n">
-        <v>995.4</v>
-      </c>
-      <c r="M134" s="4" t="n">
-        <v>1914.3</v>
-      </c>
-      <c r="N134" s="4" t="inlineStr">
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="5" t="n">
+        <v>577528.54</v>
+      </c>
+      <c r="N134" s="5" t="inlineStr">
         <is>
           <t>资金类→损益</t>
         </is>
       </c>
-      <c r="O134" s="4" t="inlineStr">
-        <is>
-          <t>到付</t>
+      <c r="O134" s="5" t="inlineStr">
+        <is>
+          <t>个人寄件三方渠道散件</t>
         </is>
       </c>
       <c r="P134" s="3" t="inlineStr"/>
@@ -9060,193 +9068,201 @@
       <c r="S134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="n">
+      <c r="A135" s="5" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>03.50</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr"/>
-      <c r="D135" s="4" t="inlineStr">
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>03.47</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>个人寄件-当日取揽件费</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>资金往来</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
+      <c r="E135" s="5" t="inlineStr">
         <is>
           <t>贷</t>
         </is>
       </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>50010614</t>
-        </is>
-      </c>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>KPI激励</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="n">
-        <v>700337</v>
-      </c>
-      <c r="I135" s="4" t="inlineStr">
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>50010104</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>总部平台单</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>700307</v>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="K135" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="L135" s="4" t="n">
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L135" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M135" s="4" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="N135" s="4" t="inlineStr">
+      <c r="M135" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N135" s="5" t="inlineStr">
         <is>
           <t>资金类→损益</t>
         </is>
       </c>
-      <c r="O135" s="4" t="inlineStr">
-        <is>
-          <t>申咚咚激励金</t>
-        </is>
-      </c>
+      <c r="O135" s="5" t="inlineStr"/>
       <c r="P135" s="3" t="inlineStr"/>
       <c r="Q135" s="3" t="inlineStr"/>
       <c r="R135" s="3" t="inlineStr"/>
       <c r="S135" s="3" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="5" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>030201</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>基础派费付费</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>总部应付</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>03.49</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr"/>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>资金往来</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>贷</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>50010201</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>基础派费</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>700308</v>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="K136" s="2" t="n">
-        <v>316</v>
-      </c>
-      <c r="L136" s="2" t="n">
-        <v>3304636.91</v>
-      </c>
-      <c r="M136" s="2" t="n">
-        <v>258.56</v>
-      </c>
-      <c r="N136" s="2" t="inlineStr"/>
-      <c r="O136" s="2" t="inlineStr"/>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>50010103</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>到付收入</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>700306</v>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>CMB</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>995.4</v>
+      </c>
+      <c r="M136" s="5" t="n">
+        <v>1914.3</v>
+      </c>
+      <c r="N136" s="5" t="inlineStr">
+        <is>
+          <t>资金类→损益</t>
+        </is>
+      </c>
+      <c r="O136" s="5" t="inlineStr">
+        <is>
+          <t>到付</t>
+        </is>
+      </c>
       <c r="P136" s="3" t="inlineStr"/>
       <c r="Q136" s="3" t="inlineStr"/>
       <c r="R136" s="3" t="inlineStr"/>
       <c r="S136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>030206</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>时效&amp;拦截弃件付费</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>总部应付</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>03.50</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr"/>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>资金往来</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
         <is>
           <t>贷</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>50010201</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>基础派费</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>700308</v>
-      </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>50010614</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>KPI激励</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>700337</v>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="K137" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>148.7</v>
-      </c>
-      <c r="M137" s="2" t="n">
+      <c r="K137" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="L137" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N137" s="2" t="inlineStr"/>
-      <c r="O137" s="2" t="inlineStr"/>
+      <c r="M137" s="5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N137" s="5" t="inlineStr">
+        <is>
+          <t>资金类→损益</t>
+        </is>
+      </c>
+      <c r="O137" s="5" t="inlineStr">
+        <is>
+          <t>申咚咚激励金</t>
+        </is>
+      </c>
       <c r="P137" s="3" t="inlineStr"/>
       <c r="Q137" s="3" t="inlineStr"/>
       <c r="R137" s="3" t="inlineStr"/>
@@ -9258,12 +9274,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>030211</t>
+          <t>030201</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>大货计重付费</t>
+          <t>基础派费付费</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -9278,16 +9294,16 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>50010203</t>
+          <t>50010201</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>大货派费</t>
+          <t>基础派费</t>
         </is>
       </c>
       <c r="H138" s="2" t="n">
-        <v>700310</v>
+        <v>700308</v>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
@@ -9300,13 +9316,13 @@
         </is>
       </c>
       <c r="K138" s="2" t="n">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>52220.37</v>
+        <v>3304636.91</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>898.99</v>
+        <v>258.56</v>
       </c>
       <c r="N138" s="2" t="inlineStr"/>
       <c r="O138" s="2" t="inlineStr"/>
@@ -9321,12 +9337,12 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>030215</t>
+          <t>030206</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>乡镇村业务付费</t>
+          <t>时效&amp;拦截弃件付费</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -9341,16 +9357,16 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>50010207</t>
+          <t>50010201</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>扶持派费</t>
+          <t>基础派费</t>
         </is>
       </c>
       <c r="H139" s="2" t="n">
-        <v>700314</v>
+        <v>700308</v>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
@@ -9363,10 +9379,10 @@
         </is>
       </c>
       <c r="K139" s="2" t="n">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>436.5</v>
+        <v>148.7</v>
       </c>
       <c r="M139" s="2" t="n">
         <v>0</v>
@@ -9384,12 +9400,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>030228</t>
+          <t>030211</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>签收考核奖励派费</t>
+          <t>大货计重付费</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -9404,16 +9420,16 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>50010608</t>
+          <t>50010203</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>签收率考核</t>
+          <t>大货派费</t>
         </is>
       </c>
       <c r="H140" s="2" t="n">
-        <v>700331</v>
+        <v>700310</v>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
@@ -9426,13 +9442,13 @@
         </is>
       </c>
       <c r="K140" s="2" t="n">
-        <v>4</v>
+        <v>271</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>464392.03</v>
+        <v>52220.37</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>0</v>
+        <v>898.99</v>
       </c>
       <c r="N140" s="2" t="inlineStr"/>
       <c r="O140" s="2" t="inlineStr"/>
@@ -9447,12 +9463,12 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>030233</t>
+          <t>030215</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>星计划奖励</t>
+          <t>乡镇村业务付费</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -9467,16 +9483,16 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>50010208</t>
+          <t>50010207</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>小件员权益</t>
+          <t>扶持派费</t>
         </is>
       </c>
       <c r="H141" s="2" t="n">
-        <v>700315</v>
+        <v>700314</v>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
@@ -9489,10 +9505,10 @@
         </is>
       </c>
       <c r="K141" s="2" t="n">
-        <v>239</v>
+        <v>112</v>
       </c>
       <c r="L141" s="2" t="n">
-        <v>8531.110000000001</v>
+        <v>436.5</v>
       </c>
       <c r="M141" s="2" t="n">
         <v>0</v>
@@ -9505,142 +9521,126 @@
       <c r="S141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="n">
+      <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>030234</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>星计划收费</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>030228</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>签收考核奖励派费</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>总部应付</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>贷</t>
         </is>
       </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>54010208</t>
-        </is>
-      </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>小件员权益</t>
-        </is>
-      </c>
-      <c r="H142" s="5" t="n">
-        <v>700349</v>
-      </c>
-      <c r="I142" s="5" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="J142" s="5" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>50010608</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>签收率考核</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>700331</v>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="K142" s="5" t="n">
+      <c r="K142" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L142" s="5" t="n">
+      <c r="L142" s="2" t="n">
+        <v>464392.03</v>
+      </c>
+      <c r="M142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M142" s="5" t="n">
-        <v>29070.41</v>
-      </c>
-      <c r="N142" s="5" t="inlineStr">
-        <is>
-          <t>负数冲减</t>
-        </is>
-      </c>
-      <c r="O142" s="5" t="inlineStr">
-        <is>
-          <t>负数，减少收入</t>
-        </is>
-      </c>
+      <c r="N142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr"/>
       <c r="P142" s="3" t="inlineStr"/>
       <c r="Q142" s="3" t="inlineStr"/>
       <c r="R142" s="3" t="inlineStr"/>
       <c r="S142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="n">
+      <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>030270</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>派费直达服务费</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>030233</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>星计划奖励</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>总部应付</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>贷</t>
         </is>
       </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>54010208</t>
-        </is>
-      </c>
-      <c r="G143" s="5" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>50010208</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>小件员权益</t>
         </is>
       </c>
-      <c r="H143" s="5" t="n">
-        <v>700349</v>
-      </c>
-      <c r="I143" s="5" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="J143" s="5" t="inlineStr">
+      <c r="H143" s="2" t="n">
+        <v>700315</v>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="K143" s="5" t="n">
-        <v>172</v>
-      </c>
-      <c r="L143" s="5" t="n">
+      <c r="K143" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>8531.110000000001</v>
+      </c>
+      <c r="M143" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M143" s="5" t="n">
-        <v>95346.98</v>
-      </c>
-      <c r="N143" s="5" t="inlineStr">
-        <is>
-          <t>负数冲减</t>
-        </is>
-      </c>
-      <c r="O143" s="5" t="inlineStr">
-        <is>
-          <t>负数，减少收入</t>
-        </is>
-      </c>
+      <c r="N143" s="2" t="inlineStr"/>
+      <c r="O143" s="2" t="inlineStr"/>
       <c r="P143" s="3" t="inlineStr"/>
       <c r="Q143" s="3" t="inlineStr"/>
       <c r="R143" s="3" t="inlineStr"/>
